--- a/research/traditional_assets/database/data/barbados/barbados_insurance_life.xlsx
+++ b/research/traditional_assets/database/data/barbados/barbados_insurance_life.xlsx
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.162</v>
+        <v>0.177</v>
       </c>
       <c r="E2">
-        <v>0.126</v>
+        <v>0.175</v>
       </c>
       <c r="G2">
-        <v>0.07114923678566923</v>
+        <v>0.1322228998322915</v>
       </c>
       <c r="H2">
-        <v>0.07114923678566923</v>
+        <v>0.1322228998322915</v>
       </c>
       <c r="I2">
-        <v>0.1249964917773301</v>
+        <v>0.1427658618392506</v>
       </c>
       <c r="J2">
-        <v>0.08986867207409917</v>
+        <v>0.09392364027789939</v>
       </c>
       <c r="K2">
-        <v>120.3</v>
+        <v>144.4</v>
       </c>
       <c r="L2">
-        <v>0.05058660275009461</v>
+        <v>0.05503887787772527</v>
       </c>
       <c r="M2">
-        <v>53.7</v>
+        <v>38.78</v>
       </c>
       <c r="N2">
-        <v>0.07595473833097596</v>
+        <v>0.06709342560553633</v>
       </c>
       <c r="O2">
-        <v>0.4463840399002494</v>
+        <v>0.2685595567867036</v>
       </c>
       <c r="P2">
-        <v>32.7</v>
+        <v>32.2</v>
       </c>
       <c r="Q2">
-        <v>0.04625176803394625</v>
+        <v>0.05570934256055364</v>
       </c>
       <c r="R2">
-        <v>0.2718204488778055</v>
+        <v>0.2229916897506925</v>
       </c>
       <c r="S2">
-        <v>21</v>
+        <v>6.579999999999998</v>
       </c>
       <c r="T2">
-        <v>0.3910614525139665</v>
+        <v>0.1696750902527075</v>
       </c>
       <c r="U2">
-        <v>351.5</v>
+        <v>336.9</v>
       </c>
       <c r="V2">
-        <v>0.4971711456859972</v>
+        <v>0.5828719723183391</v>
       </c>
       <c r="W2">
-        <v>0.1131277035922513</v>
+        <v>0.1271350589892587</v>
       </c>
       <c r="X2">
-        <v>0.3887984012768098</v>
+        <v>0.6480864945900302</v>
       </c>
       <c r="Y2">
-        <v>-0.2756706976845585</v>
+        <v>-0.5209514356007715</v>
       </c>
       <c r="Z2">
-        <v>1.087828029122802</v>
+        <v>1.052607327281705</v>
       </c>
       <c r="AA2">
-        <v>0.09776166042225073</v>
+        <v>0.09886471196148798</v>
       </c>
       <c r="AB2">
-        <v>0.1720473819287881</v>
+        <v>0.254362009836627</v>
       </c>
       <c r="AC2">
-        <v>-0.07428572150653739</v>
+        <v>-0.1554972978751391</v>
       </c>
       <c r="AD2">
-        <v>1707.9</v>
+        <v>1850.5</v>
       </c>
       <c r="AE2">
-        <v>0.3992145216564014</v>
+        <v>0.277424392711287</v>
       </c>
       <c r="AF2">
-        <v>1708.299214521656</v>
+        <v>1850.777424392711</v>
       </c>
       <c r="AG2">
-        <v>1356.799214521656</v>
+        <v>1513.877424392711</v>
       </c>
       <c r="AH2">
-        <v>0.7072826440097942</v>
+        <v>0.7620201858782829</v>
       </c>
       <c r="AI2">
-        <v>0.5027072006907409</v>
+        <v>0.5648680532983527</v>
       </c>
       <c r="AJ2">
-        <v>0.6574279149709497</v>
+        <v>0.7236931795046271</v>
       </c>
       <c r="AK2">
-        <v>0.4453341531237042</v>
+        <v>0.5149983163670077</v>
       </c>
       <c r="AL2">
-        <v>42.2</v>
+        <v>56.8</v>
       </c>
       <c r="AM2">
-        <v>42.2</v>
+        <v>56.8</v>
       </c>
       <c r="AN2">
-        <v>5.4385830833604</v>
+        <v>4.713256719033356</v>
       </c>
       <c r="AO2">
-        <v>7.035545023696682</v>
+        <v>6.589788732394367</v>
       </c>
       <c r="AP2">
-        <v>4.320548776634556</v>
+        <v>3.855872976120972</v>
       </c>
       <c r="AQ2">
-        <v>7.035545023696682</v>
+        <v>6.589788732394367</v>
       </c>
     </row>
     <row r="3">
@@ -722,121 +722,121 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.162</v>
+        <v>0.177</v>
       </c>
       <c r="E3">
-        <v>0.126</v>
+        <v>0.175</v>
       </c>
       <c r="G3">
-        <v>0.07114923678566923</v>
+        <v>0.1322228998322915</v>
       </c>
       <c r="H3">
-        <v>0.07114923678566923</v>
+        <v>0.1322228998322915</v>
       </c>
       <c r="I3">
-        <v>0.1249964917773301</v>
+        <v>0.1427658618392506</v>
       </c>
       <c r="J3">
-        <v>0.08986867207409917</v>
+        <v>0.09392364027789939</v>
       </c>
       <c r="K3">
-        <v>120.3</v>
+        <v>144.4</v>
       </c>
       <c r="L3">
-        <v>0.05058660275009461</v>
+        <v>0.05503887787772527</v>
       </c>
       <c r="M3">
-        <v>53.7</v>
+        <v>38.78</v>
       </c>
       <c r="N3">
-        <v>0.07595473833097596</v>
+        <v>0.06709342560553633</v>
       </c>
       <c r="O3">
-        <v>0.4463840399002494</v>
+        <v>0.2685595567867036</v>
       </c>
       <c r="P3">
-        <v>32.7</v>
+        <v>32.2</v>
       </c>
       <c r="Q3">
-        <v>0.04625176803394625</v>
+        <v>0.05570934256055364</v>
       </c>
       <c r="R3">
-        <v>0.2718204488778055</v>
+        <v>0.2229916897506925</v>
       </c>
       <c r="S3">
-        <v>21</v>
+        <v>6.579999999999998</v>
       </c>
       <c r="T3">
-        <v>0.3910614525139665</v>
+        <v>0.1696750902527075</v>
       </c>
       <c r="U3">
-        <v>351.5</v>
+        <v>336.9</v>
       </c>
       <c r="V3">
-        <v>0.4971711456859972</v>
+        <v>0.5828719723183391</v>
       </c>
       <c r="W3">
-        <v>0.1131277035922513</v>
+        <v>0.1271350589892587</v>
       </c>
       <c r="X3">
-        <v>0.3887984012768098</v>
+        <v>0.6480864945900302</v>
       </c>
       <c r="Y3">
-        <v>-0.2756706976845585</v>
+        <v>-0.5209514356007715</v>
       </c>
       <c r="Z3">
-        <v>1.087828029122802</v>
+        <v>1.052607327281705</v>
       </c>
       <c r="AA3">
-        <v>0.09776166042225073</v>
+        <v>0.09886471196148798</v>
       </c>
       <c r="AB3">
-        <v>0.1720473819287881</v>
+        <v>0.254362009836627</v>
       </c>
       <c r="AC3">
-        <v>-0.07428572150653739</v>
+        <v>-0.1554972978751391</v>
       </c>
       <c r="AD3">
-        <v>1707.9</v>
+        <v>1850.5</v>
       </c>
       <c r="AE3">
-        <v>0.3992145216564014</v>
+        <v>0.277424392711287</v>
       </c>
       <c r="AF3">
-        <v>1708.299214521656</v>
+        <v>1850.777424392711</v>
       </c>
       <c r="AG3">
-        <v>1356.799214521656</v>
+        <v>1513.877424392711</v>
       </c>
       <c r="AH3">
-        <v>0.7072826440097942</v>
+        <v>0.7620201858782829</v>
       </c>
       <c r="AI3">
-        <v>0.5027072006907409</v>
+        <v>0.5648680532983527</v>
       </c>
       <c r="AJ3">
-        <v>0.6574279149709497</v>
+        <v>0.7236931795046271</v>
       </c>
       <c r="AK3">
-        <v>0.4453341531237042</v>
+        <v>0.5149983163670077</v>
       </c>
       <c r="AL3">
-        <v>42.2</v>
+        <v>56.8</v>
       </c>
       <c r="AM3">
-        <v>42.2</v>
+        <v>56.8</v>
       </c>
       <c r="AN3">
-        <v>5.4385830833604</v>
+        <v>4.713256719033356</v>
       </c>
       <c r="AO3">
-        <v>7.035545023696682</v>
+        <v>6.589788732394367</v>
       </c>
       <c r="AP3">
-        <v>4.320548776634556</v>
+        <v>3.855872976120972</v>
       </c>
       <c r="AQ3">
-        <v>7.035545023696682</v>
+        <v>6.589788732394367</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/barbados/barbados_insurance_life.xlsx
+++ b/research/traditional_assets/database/data/barbados/barbados_insurance_life.xlsx
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.177</v>
+        <v>0.172</v>
       </c>
       <c r="E2">
-        <v>0.175</v>
+        <v>0.518</v>
       </c>
       <c r="G2">
-        <v>0.1322228998322915</v>
+        <v>0.1266343420832637</v>
       </c>
       <c r="H2">
-        <v>0.1322228998322915</v>
+        <v>0.1266343420832637</v>
       </c>
       <c r="I2">
-        <v>0.1427658618392506</v>
+        <v>0.2489334312582219</v>
       </c>
       <c r="J2">
-        <v>0.09392364027789939</v>
+        <v>0.1960365878787033</v>
       </c>
       <c r="K2">
-        <v>144.4</v>
+        <v>398.6</v>
       </c>
       <c r="L2">
-        <v>0.05503887787772527</v>
+        <v>0.1332887477010533</v>
       </c>
       <c r="M2">
-        <v>38.78</v>
+        <v>37.18</v>
       </c>
       <c r="N2">
-        <v>0.06709342560553633</v>
+        <v>0.0581391712275215</v>
       </c>
       <c r="O2">
-        <v>0.2685595567867036</v>
+        <v>0.09327646763672855</v>
       </c>
       <c r="P2">
-        <v>32.2</v>
+        <v>32.1</v>
       </c>
       <c r="Q2">
-        <v>0.05570934256055364</v>
+        <v>0.05019546520719312</v>
       </c>
       <c r="R2">
-        <v>0.2229916897506925</v>
+        <v>0.08053186151530356</v>
       </c>
       <c r="S2">
-        <v>6.579999999999998</v>
+        <v>5.079999999999998</v>
       </c>
       <c r="T2">
-        <v>0.1696750902527075</v>
+        <v>0.1366325981710597</v>
       </c>
       <c r="U2">
-        <v>336.9</v>
+        <v>388.3</v>
       </c>
       <c r="V2">
-        <v>0.5828719723183391</v>
+        <v>0.6071931196247068</v>
       </c>
       <c r="W2">
-        <v>0.1271350589892587</v>
+        <v>0.3853814173837378</v>
       </c>
       <c r="X2">
-        <v>0.6480864945900302</v>
+        <v>0.2600833260987013</v>
       </c>
       <c r="Y2">
-        <v>-0.5209514356007715</v>
+        <v>0.1252980912850366</v>
       </c>
       <c r="Z2">
-        <v>1.052607327281705</v>
+        <v>1.173643570928225</v>
       </c>
       <c r="AA2">
-        <v>0.09886471196148798</v>
+        <v>0.230077081030546</v>
       </c>
       <c r="AB2">
-        <v>0.254362009836627</v>
+        <v>0.1820825297984703</v>
       </c>
       <c r="AC2">
-        <v>-0.1554972978751391</v>
+        <v>0.04799455123207574</v>
       </c>
       <c r="AD2">
-        <v>1850.5</v>
+        <v>686.9</v>
       </c>
       <c r="AE2">
-        <v>0.277424392711287</v>
+        <v>0.1478691114368103</v>
       </c>
       <c r="AF2">
-        <v>1850.777424392711</v>
+        <v>687.0478691114367</v>
       </c>
       <c r="AG2">
-        <v>1513.877424392711</v>
+        <v>298.7478691114367</v>
       </c>
       <c r="AH2">
-        <v>0.7620201858782829</v>
+        <v>0.5179216559833931</v>
       </c>
       <c r="AI2">
-        <v>0.5648680532983527</v>
+        <v>0.4740393136484554</v>
       </c>
       <c r="AJ2">
-        <v>0.7236931795046271</v>
+        <v>0.3184103891377494</v>
       </c>
       <c r="AK2">
-        <v>0.5149983163670077</v>
+        <v>0.2815592753243263</v>
       </c>
       <c r="AL2">
-        <v>56.8</v>
+        <v>89.8</v>
       </c>
       <c r="AM2">
-        <v>56.8</v>
+        <v>89.8</v>
       </c>
       <c r="AN2">
-        <v>4.713256719033356</v>
+        <v>0.9079193459914218</v>
       </c>
       <c r="AO2">
-        <v>6.589788732394367</v>
+        <v>8.288418708240535</v>
       </c>
       <c r="AP2">
-        <v>3.855872976120972</v>
+        <v>0.3948740281554615</v>
       </c>
       <c r="AQ2">
-        <v>6.589788732394367</v>
+        <v>8.288418708240535</v>
       </c>
     </row>
     <row r="3">
@@ -722,121 +722,121 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.177</v>
+        <v>0.172</v>
       </c>
       <c r="E3">
-        <v>0.175</v>
+        <v>0.518</v>
       </c>
       <c r="G3">
-        <v>0.1322228998322915</v>
+        <v>0.1266343420832637</v>
       </c>
       <c r="H3">
-        <v>0.1322228998322915</v>
+        <v>0.1266343420832637</v>
       </c>
       <c r="I3">
-        <v>0.1427658618392506</v>
+        <v>0.2489334312582219</v>
       </c>
       <c r="J3">
-        <v>0.09392364027789939</v>
+        <v>0.1960365878787033</v>
       </c>
       <c r="K3">
-        <v>144.4</v>
+        <v>398.6</v>
       </c>
       <c r="L3">
-        <v>0.05503887787772527</v>
+        <v>0.1332887477010533</v>
       </c>
       <c r="M3">
-        <v>38.78</v>
+        <v>37.18</v>
       </c>
       <c r="N3">
-        <v>0.06709342560553633</v>
+        <v>0.0581391712275215</v>
       </c>
       <c r="O3">
-        <v>0.2685595567867036</v>
+        <v>0.09327646763672855</v>
       </c>
       <c r="P3">
-        <v>32.2</v>
+        <v>32.1</v>
       </c>
       <c r="Q3">
-        <v>0.05570934256055364</v>
+        <v>0.05019546520719312</v>
       </c>
       <c r="R3">
-        <v>0.2229916897506925</v>
+        <v>0.08053186151530356</v>
       </c>
       <c r="S3">
-        <v>6.579999999999998</v>
+        <v>5.079999999999998</v>
       </c>
       <c r="T3">
-        <v>0.1696750902527075</v>
+        <v>0.1366325981710597</v>
       </c>
       <c r="U3">
-        <v>336.9</v>
+        <v>388.3</v>
       </c>
       <c r="V3">
-        <v>0.5828719723183391</v>
+        <v>0.6071931196247068</v>
       </c>
       <c r="W3">
-        <v>0.1271350589892587</v>
+        <v>0.3853814173837378</v>
       </c>
       <c r="X3">
-        <v>0.6480864945900302</v>
+        <v>0.2600833260987013</v>
       </c>
       <c r="Y3">
-        <v>-0.5209514356007715</v>
+        <v>0.1252980912850366</v>
       </c>
       <c r="Z3">
-        <v>1.052607327281705</v>
+        <v>1.173643570928225</v>
       </c>
       <c r="AA3">
-        <v>0.09886471196148798</v>
+        <v>0.230077081030546</v>
       </c>
       <c r="AB3">
-        <v>0.254362009836627</v>
+        <v>0.1820825297984703</v>
       </c>
       <c r="AC3">
-        <v>-0.1554972978751391</v>
+        <v>0.04799455123207574</v>
       </c>
       <c r="AD3">
-        <v>1850.5</v>
+        <v>686.9</v>
       </c>
       <c r="AE3">
-        <v>0.277424392711287</v>
+        <v>0.1478691114368103</v>
       </c>
       <c r="AF3">
-        <v>1850.777424392711</v>
+        <v>687.0478691114367</v>
       </c>
       <c r="AG3">
-        <v>1513.877424392711</v>
+        <v>298.7478691114367</v>
       </c>
       <c r="AH3">
-        <v>0.7620201858782829</v>
+        <v>0.5179216559833931</v>
       </c>
       <c r="AI3">
-        <v>0.5648680532983527</v>
+        <v>0.4740393136484554</v>
       </c>
       <c r="AJ3">
-        <v>0.7236931795046271</v>
+        <v>0.3184103891377494</v>
       </c>
       <c r="AK3">
-        <v>0.5149983163670077</v>
+        <v>0.2815592753243263</v>
       </c>
       <c r="AL3">
-        <v>56.8</v>
+        <v>89.8</v>
       </c>
       <c r="AM3">
-        <v>56.8</v>
+        <v>89.8</v>
       </c>
       <c r="AN3">
-        <v>4.713256719033356</v>
+        <v>0.9079193459914218</v>
       </c>
       <c r="AO3">
-        <v>6.589788732394367</v>
+        <v>8.288418708240535</v>
       </c>
       <c r="AP3">
-        <v>3.855872976120972</v>
+        <v>0.3948740281554615</v>
       </c>
       <c r="AQ3">
-        <v>6.589788732394367</v>
+        <v>8.288418708240535</v>
       </c>
     </row>
   </sheetData>
